--- a/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
+++ b/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
@@ -443,14 +443,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
           <t>Examples</t>
@@ -458,24 +458,24 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Comment</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BCIO:050557</t>
+          <t>BCIO:011000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>social influence intervention through mass media</t>
+          <t>behaviour change intervention mode of delivery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -484,33 +484,38 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A behaviour change intervention that is an awareness of other people’s thoughts, feelings and actions BCT delivered through a mass media mode of delivery.</t>
+          <t>An attribute of a BCI delivery that is the physical or informational medium through which a BCI is provided.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BCI mode of delivery</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCIO:011000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>behaviour change intervention mode of delivery</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>BCIO:011065</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>arts feature mode of delivery</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>An attribute of a BCI delivery that is the physical or informational medium through which a BCI is provided.</t>
+          <t>Mode of delivery that involves application of creativity on the part of the intervention recipient.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -520,7 +525,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>BCI mode of delivery</t>
+          <t>Includes art therapy, music therapy, dance and acting.</t>
         </is>
       </c>
     </row>
@@ -549,7 +554,7 @@
           <t>Mode of delivery</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>This does not include use of textual or pictorial information. It includes lighting, speed humps, use of music, shape and size of containers of consumables.</t>
         </is>
@@ -558,13 +563,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCIO:011064</t>
+          <t>BCIO:011062</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gamification mode of delivery</t>
+          <t>push mode of delivery</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -572,30 +577,25 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves application of typical elements of game playing  to other areas of activity, typically as an online marketing technique to encourage engagement with a product or service.</t>
+          <t>Mode of delivery that is not dependent on actions on the part of the intervention recipient.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Includes point scoring, competition with others, and rules of play.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:011062</t>
+          <t>BCIO:011063</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>push mode of delivery</t>
+          <t>pull mode of delivery</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -603,7 +603,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mode of delivery that is not dependent on actions on the part of the intervention recipient.</t>
+          <t>Mode of delivery that requires some action on the part of the recipient.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -615,13 +615,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:011056</t>
+          <t>BCIO:011055</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pair-based mode of delivery</t>
+          <t>individual-based mode of delivery</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -629,7 +629,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves two recipients in the location where the intervention is delivered who have an interpersonal relationship.</t>
+          <t>Mode of delivery that involves one recipient in the location where the intervention is delivered.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -641,13 +641,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:011058</t>
+          <t>BCIO:011054</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>uni-directional mode of delivery</t>
+          <t>somatic alteration mode of delivery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -655,25 +655,30 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mode of delivery in which the only causal influence is from the intervention source to the recipient.</t>
+          <t>Mode of of delivery that involves modifying the structure of the body of the recipient of the intervention.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Includes surgery.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:011060</t>
+          <t>BCIO:011056</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>synchronous mode of delivery</t>
+          <t>pair-based mode of delivery</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -681,7 +686,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves delivery and receipt of the intervention or its components occurring at the same time or very close in time.</t>
+          <t>Mode of delivery that involves two recipients in the location where the intervention is delivered who have an interpersonal relationship.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -693,13 +698,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:011061</t>
+          <t>BCIO:011034</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>asynchronous mode of delivery</t>
+          <t>somatic mode of delivery</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -707,7 +712,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves receipt of the intervention or its components taking place a significant period of time after delivery.</t>
+          <t>Mode of delivery that involves devices or substances that alter bodily processes or structure.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -719,21 +724,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:011034</t>
+          <t>BCIO:011035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>somatic mode of delivery</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ingestion mode of delivery</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves devices or substances that alter bodily processes or structure.</t>
+          <t>Somatic mode of delivery that involves ingestion of a chemical into the body.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -745,21 +750,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:011048</t>
+          <t>BCIO:011037</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>physical stimulus mode of delivery</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>alimentary mode of delivery</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A mode of delivery that involves application of a physical stimulus to the body.</t>
+          <t>Somatic mode of delivery that involves ingestion of a chemical through the stomach or intestine.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -771,52 +776,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:011052</t>
+          <t>BCIO:011039</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>physical pressure mode of delivery</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ingestable liquid mode of delivery</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves application of physical pressure to the outside of the body.</t>
+          <t>Alimentary mode of delivery that involves swallowing of a liquid.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Includes massage.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:011050</t>
+          <t>BCIO:011038</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>temperature mode of delivery</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pill mode of delivery</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Physical stimulius mode of delivery that involves application of heat or cold to the body.</t>
+          <t>Alimentary mode of delivery that involves swallowing of a pill or oral capsule.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:011049</t>
+          <t>BCIO:011036</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -836,30 +836,25 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>light exposure mode of delivery</t>
+          <t>transdermal mode of delivery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves exposure of light to the body</t>
+          <t>Ingestion mode of delivery that involves ingestion of a chemical through the skin.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Includes photo therapy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:011051</t>
+          <t>BCIO:011040</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -867,13 +862,13 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>electrical stimulation mode of delivery</t>
+          <t>buccal mode of delivery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves application of electrical stimulation to the body.</t>
+          <t>Ingestion mode of delivery that involves absorption of a chemical through the lining of the buccal cavity.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -885,7 +880,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:011053</t>
+          <t>BCIO:011046</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -893,39 +888,44 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>wearable stimulus mode of delivery</t>
+          <t>wearable ingestion mode of delivery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves a device that is worn on the body.</t>
+          <t>Ingestion mode of delivery that involves a device that is worn on the body.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Includes insulin pump.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:011035</t>
+          <t>BCIO:011041</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ingestion mode of delivery</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>inhalation mode of delivery</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Somatic mode of delivery that involves ingestion of a chemical into the body.</t>
+          <t>Ingestion mode of delivery that involves absorption of a chemical through  the upper airways or lungs by inspiration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:011036</t>
+          <t>BCIO:011042</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -945,13 +945,13 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>transdermal mode of delivery</t>
+          <t>injection mode of delivery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves ingestion of a chemical through the skin.</t>
+          <t>Ingestion mode of delivery that involves a chemical being introduced into body tissue through a hollow needle that punctures the skin.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -963,52 +963,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:011046</t>
+          <t>BCIO:011045</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>wearable ingestion mode of delivery</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>intramuscular injection mode of delivery</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves a device that is worn on the body.</t>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is muscle.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Includes insulin pump.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:011042</t>
+          <t>BCIO:011043</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>injection mode of delivery</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>subcutaneous injection mode of delivery</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves a chemical being introduced into body tissue through a hollow needle that punctures the skin.</t>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is subcutaneous tissue.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1020,7 +1015,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:011043</t>
+          <t>BCIO:011044</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1029,12 +1024,12 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>subcutaneous injection mode of delivery</t>
+          <t>intravenous injection mode of delivery</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is subcutaneous tissue.</t>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is venous blood.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1046,21 +1041,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:011044</t>
+          <t>BCIO:011048</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>physical stimulus mode of delivery</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>intravenous injection mode of delivery</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is venous blood.</t>
+          <t>A mode of delivery that involves application of a physical stimulus to the body.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1072,21 +1067,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:011045</t>
+          <t>BCIO:011051</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>intramuscular injection mode of delivery</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>electrical stimulation mode of delivery</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is muscle.</t>
+          <t>Physical stimulus mode of delivery that involves application of electrical stimulation to the body.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1098,7 +1093,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:011041</t>
+          <t>BCIO:011049</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1106,25 +1101,30 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>inhalation mode of delivery</t>
+          <t>light exposure mode of delivery</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves absorption of a chemical through  the upper airways or lungs by inspiration.</t>
+          <t>Physical stimulus mode of delivery that involves exposure of light to the body</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Includes photo therapy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:011037</t>
+          <t>BCIO:011053</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>alimentary mode of delivery</t>
+          <t>wearable stimulus mode of delivery</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Somatic mode of delivery that involves ingestion of a chemical through the stomach or intestine.</t>
+          <t>Physical stimulus mode of delivery that involves a device that is worn on the body.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1150,21 +1150,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:011038</t>
+          <t>BCIO:011050</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>pill mode of delivery</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>temperature mode of delivery</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alimentary mode of delivery that involves swallowing of a pill or oral capsule.</t>
+          <t>Physical stimulius mode of delivery that involves application of heat or cold to the body.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1176,73 +1176,83 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:011039</t>
+          <t>BCIO:011052</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ingestable liquid mode of delivery</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>physical pressure mode of delivery</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alimentary mode of delivery that involves swallowing of a liquid.</t>
+          <t>Physical stimulus mode of delivery that involves application of physical pressure to the outside of the body.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Includes massage.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:011040</t>
+          <t>BCIO:011047</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>buccal mode of delivery</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>chewable substance mode of delivery</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves absorption of a chemical through the lining of the buccal cavity.</t>
+          <t>Ingestion mode of delivery that involves chewing of a soft material.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>This includes chewing gum. often involves ingestion of a chemical that is released by chewing and absorbed through the lining of the buccal cavity, but this is not necessary.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:011047</t>
+          <t>BCIO:011001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>chewable substance mode of delivery</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>informational mode of delivery</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves chewing of a soft material.</t>
+          <t>Mode of delivery that involves intentional transmission of a representation of the world to an intervention recipient with the aim of changing that person's representation of the world.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1250,73 +1260,73 @@
           <t>Mode of delivery</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>This includes chewing gum. often involves ingestion of a chemical that is released by chewing and absorbed through the lining of the buccal cavity, but this is not necessary.</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>This includes delivery of rewards, prompts, and cues that result in learning and information about the environment and environmental contingencies.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:011001</t>
+          <t>BCIO:011032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>informational mode of delivery</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>textual mode of delivery</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves intentional transmission of a representation of the world to an intervention recipient with the aim of changing that person's representation of the world.</t>
+          <t>Informational mode of delivery that involves written text.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>This includes delivery of rewards, prompts, and cues that result in learning and information about the environment and environmental contingencies.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:011002</t>
+          <t>BCIO:011005</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>human interactional mode of delivery</t>
+          <t>printed material mode of delivery</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves a person as intervention source who interacts with an intervention recipient in real time.</t>
+          <t>Informational mode of delivery that involves use of printed material.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Can include paper, acetate, text, diagrams and photographic images.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:011004</t>
+          <t>BCIO:011008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1324,25 +1334,30 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>at-a-distance mode of delivery</t>
+          <t>printed publication mode of delivery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Human interactional mode of delivery that involves an intervention source and recipient being in different locations and communicating through a communication channel.</t>
+          <t>Printed material mode of delivery that involves use of of a printed publication.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Includes leaflets, brochures, newspapers, newsletter, booklets, magazines, manuals or worksheets.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:011003</t>
+          <t>BCIO:011006</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1350,13 +1365,13 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>face to face mode of delivery</t>
+          <t>letter mode of delivery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Human interactional mode of delivery that involves an intervention source and recipient being together in the same location and communicating directly.</t>
+          <t>Printed material mode of delivery that involves a letter or postcard that can be sent through the post or handed directly to the recipient</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1368,21 +1383,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:011010</t>
+          <t>BCIO:011007</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>electronic mode of delivery</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public notice mode of delivery</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves electronic technology in the presentation of information to an intervention recipient.</t>
+          <t>Printed material mode of delivery that involves display of a poster, sign or notice in a public location.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1394,7 +1409,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:011017</t>
+          <t>BCIO:011009</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1402,44 +1417,39 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3-D projection mode of delivery</t>
+          <t>labelling mode of delivery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of a 3-D image.</t>
+          <t>Printed material mode of delivery that involves information printed on a product or its packaging, or a label attached to or included with, a product or its packaging, and aims to convey information about that product.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Includes hologram but does not include virtual reality headsets.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:011028</t>
+          <t>BCIO:011010</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>mobile application mode of delivery</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>electronic mode of delivery</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient interacting with a mobile application.</t>
+          <t>Informational mode of delivery that involves electronic technology in the presentation of information to an intervention recipient.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1451,7 +1461,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:011025</t>
+          <t>BCIO:011016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1459,25 +1469,30 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>email mode of delivery</t>
+          <t>electronic environmental object mode of delivery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves communication by email.</t>
+          <t>Electronic mode of delivery that involves an electronic device positioned in the environment of the intervention recipient that can gather information and respond to commands.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Includes robots, and 'internet of things'.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:011014</t>
+          <t>BCIO:011012</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1485,13 +1500,13 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>electronic billboard mode of delivery</t>
+          <t>mobile digital device mode of delivery</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by an electronic screen positioned in a public location.</t>
+          <t>Electronic mode of delivery that involves presentation of information by a handheld mobile digital device that can store, retrieve and process data.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1503,7 +1518,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:011026</t>
+          <t>BCIO:011015</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1511,25 +1526,30 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>video game mode of delivery</t>
+          <t>wearable electronic device mode of delivery</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient playing a computer game.</t>
+          <t>Electronic mode of delivery that involves presentation of information by an electronic device that is worn or carried on the body.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Includes a watch, clip-on device, spectacles, in-ear devfice, vibrating device.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:011029</t>
+          <t>BCIO:011025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1537,13 +1557,13 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>e-book mode of delivery</t>
+          <t>email mode of delivery</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient being given access to an e-book.</t>
+          <t>Electronic mode of delivery that involves communication by email.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1555,7 +1575,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:011019</t>
+          <t>BCIO:011028</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1563,30 +1583,25 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>playable electronic storage mode of delivery</t>
+          <t>mobile application mode of delivery</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information stored on an object that is inserted into a playing device.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient interacting with a mobile application.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Includes cassettes, video tapes, DVDs, CDs.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:011016</t>
+          <t>BCIO:011029</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1594,30 +1609,25 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>electronic environmental object mode of delivery</t>
+          <t>e-book mode of delivery</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves an electronic device positioned in the environment of the intervention recipient that can gather information and respond to commands.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient being given access to an e-book.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Includes robots, and 'internet of things'.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:011015</t>
+          <t>BCIO:011013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1625,30 +1635,25 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>wearable electronic device mode of delivery</t>
+          <t>computer mode of delivery</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by an electronic device that is worn or carried on the body.</t>
+          <t>Electronic mode of delivery that involves presentation of information by a desktop or laptop computer.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Includes a watch, clip-on device, spectacles, in-ear devfice, vibrating device.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:011020</t>
+          <t>BCIO:050558</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1656,30 +1661,25 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>radio broadcast mode of delivery</t>
+          <t>online press mode of delivery</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of audio information that is broadcast and received by a radio receiver.</t>
+          <t>Electronic mode of delivery of a newspaper or magazine.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Includes digital radio and audio that is streamed as a podcast.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:011013</t>
+          <t>BCIO:011026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1687,13 +1687,13 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>computer mode of delivery</t>
+          <t>video game mode of delivery</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by a desktop or laptop computer.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient playing a computer game.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:011018</t>
+          <t>BCIO:011021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>virtual reality mode of delivery</t>
+          <t>call mode of delivery</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves use of virtual reality through a virtual reality headset and optionally body movement sensors.</t>
+          <t>Electronic mode of delivery that involves a communication process in which a signal is sent by a caller to a recipient to alert them of the communication intent, giving the recipient the opportunity to enage with the communication.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1731,47 +1731,52 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:011027</t>
+          <t>BCIO:011024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>website mode of delivery</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>messaging mode of delivery</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient interacting with a website.</t>
+          <t>Call mode of delivery that involves textual information in the communication.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Text message can include emojis, and additional audio and pictorial material. Includes SMS, WhatsApp and other messaging services.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:011011</t>
+          <t>BCIO:011022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>television mode of delivery</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>audio call mode of delivery</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information that is broadcast and displayed by television.</t>
+          <t>Call mode of delivery that involves only audio information in the communication.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1779,30 +1784,30 @@
           <t>Mode of delivery</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Includes internet and satellite television.</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Includes automated calls and audio messaging.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:011012</t>
+          <t>BCIO:011023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>mobile digital device mode of delivery</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>video call mode of delivery</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by a handheld mobile digital device that can store, retrieve and process data.</t>
+          <t>Call mode of delivery that involves video and audio information in the communication.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -1814,7 +1819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:050558</t>
+          <t>BCIO:011017</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1822,25 +1827,30 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>online press mode of delivery</t>
+          <t>3-D projection mode of delivery</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery of a newspaper or magazine.</t>
+          <t>Electronic mode of delivery that involves presentation of a 3-D image.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Includes hologram but does not include virtual reality headsets.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:011021</t>
+          <t>BCIO:011018</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1848,13 +1858,13 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>call mode of delivery</t>
+          <t>virtual reality mode of delivery</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves a communication process in which a signal is sent by a caller to a recipient to alert them of the communication intent, giving the recipient the opportunity to enage with the communication.</t>
+          <t>Electronic mode of delivery that involves use of virtual reality through a virtual reality headset and optionally body movement sensors.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -1866,78 +1876,78 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:011022</t>
+          <t>BCIO:011014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>audio call mode of delivery</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>electronic billboard mode of delivery</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves only audio information in the communication.</t>
+          <t>Electronic mode of delivery that involves presentation of information by an electronic screen positioned in a public location.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Includes automated calls and audio messaging.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:011023</t>
+          <t>BCIO:011019</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>video call mode of delivery</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>playable electronic storage mode of delivery</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves video and audio information in the communication.</t>
+          <t>Electronic mode of delivery that involves presentation of information stored on an object that is inserted into a playing device.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Includes cassettes, video tapes, DVDs, CDs.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:011024</t>
+          <t>BCIO:011011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>messaging mode of delivery</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>television mode of delivery</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves textual information in the communication.</t>
+          <t>Electronic mode of delivery that involves presentation of information that is broadcast and displayed by television.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -1945,47 +1955,42 @@
           <t>Mode of delivery</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Text message can include emojis, and additional audio and pictorial material. Includes SMS, WhatsApp and other messaging services.</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Includes internet and satellite television.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:011005</t>
+          <t>BCIO:011027</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>printed material mode of delivery</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>website mode of delivery</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves use of printed material.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient interacting with a website.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Can include paper, acetate, text, diagrams and photographic images.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:011006</t>
+          <t>BCIO:011020</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1993,39 +1998,44 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>letter mode of delivery</t>
+          <t>radio broadcast mode of delivery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves a letter or postcard that can be sent through the post or handed directly to the recipient</t>
+          <t>Electronic mode of delivery that involves presentation of audio information that is broadcast and received by a radio receiver.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Includes digital radio and audio that is streamed as a podcast.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:011009</t>
+          <t>BCIO:011030</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>labelling mode of delivery</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>audio informational mode of delivery</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves information printed on a product or its packaging, or a label attached to or included with, a product or its packaging, and aims to convey information about that product.</t>
+          <t>Informational mode of delivery that involves sound.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2037,109 +2047,104 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:011008</t>
+          <t>BCIO:011031</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>printed publication mode of delivery</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>visual informational mode of delivery</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves use of of a printed publication.</t>
+          <t>Informational mode of delivery that involves visual images.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Includes leaflets, brochures, newspapers, newsletter, booklets, magazines, manuals or worksheets.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:011007</t>
+          <t>BCIO:050556</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>public notice mode of delivery</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mass media mode of delivery</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves display of a poster, sign or notice in a public location.</t>
+          <t>Informational mode of delivery of radio broadcast, television, online press and printed press to a mass audience.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>This is a form of mass media.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:050556</t>
+          <t>BCIO:011002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>mass media mode of delivery</t>
+          <t>human interactional mode of delivery</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Informational mode of delivery of radio broadcast, television, online press and printed press to a mass audience.</t>
+          <t>Informational mode of delivery that involves a person as intervention source who interacts with an intervention recipient in real time.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>This is a form of mass media.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:011030</t>
+          <t>BCIO:011003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>audio informational mode of delivery</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>face to face mode of delivery</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves sound.</t>
+          <t>Human interactional mode of delivery that involves an intervention source and recipient being together in the same location and communicating directly.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2151,21 +2156,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:011032</t>
+          <t>BCIO:011004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>textual mode of delivery</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>at-a-distance mode of delivery</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves written text.</t>
+          <t>Human interactional mode of delivery that involves an intervention source and recipient being in different locations and communicating through a communication channel.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2177,39 +2182,44 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:011031</t>
+          <t>BCIO:011064</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>visual informational mode of delivery</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gamification mode of delivery</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves visual images.</t>
+          <t>Mode of delivery that involves application of typical elements of game playing  to other areas of activity, typically as an online marketing technique to encourage engagement with a product or service.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Includes point scoring, competition with others, and rules of play.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:011063</t>
+          <t>BCIO:011060</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>pull mode of delivery</t>
+          <t>synchronous mode of delivery</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2217,7 +2227,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Mode of delivery that requires some action on the part of the recipient.</t>
+          <t>Mode of delivery that involves delivery and receipt of the intervention or its components occurring at the same time or very close in time.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2229,13 +2239,13 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:011065</t>
+          <t>BCIO:011058</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>arts feature mode of delivery</t>
+          <t>uni-directional mode of delivery</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2243,30 +2253,25 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves application of creativity on the part of the intervention recipient.</t>
+          <t>Mode of delivery in which the only causal influence is from the intervention source to the recipient.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Includes art therapy, music therapy, dance and acting.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:011054</t>
+          <t>BCIO:011061</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>somatic alteration mode of delivery</t>
+          <t>asynchronous mode of delivery</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2274,17 +2279,12 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mode of of delivery that involves modifying the structure of the body of the recipient of the intervention.</t>
+          <t>Mode of delivery that involves receipt of the intervention or its components taking place a significant period of time after delivery.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Includes surgery.</t>
         </is>
       </c>
     </row>
@@ -2317,13 +2317,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:011055</t>
+          <t>BCIO:011059</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>individual-based mode of delivery</t>
+          <t>interactional mode of delivery</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves one recipient in the location where the intervention is delivered.</t>
+          <t>Mode of delivery in which there is causal influence from the intervention source to the recipient and from the recipient to the source.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2343,21 +2343,21 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:011059</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>interactional mode of delivery</t>
-        </is>
-      </c>
+          <t>BCIO:050557</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>social influence intervention through mass media</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mode of delivery in which there is causal influence from the intervention source to the recipient and from the recipient to the source.</t>
+          <t>A behaviour change intervention that is an awareness of other people’s thoughts, feelings and actions BCT delivered through a mass media mode of delivery.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">

--- a/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
+++ b/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
@@ -520,7 +520,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>realizable entity</t>
+          <t>realizable</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A disposition that inheres in some extended organism.</t>
+          <t>A &lt;disposition&gt; that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">A mental disposition is a bodily disposition that is realized in a mental process. </t>
+          <t>A bodily disposition that is realized in a mental process.</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>fiat object</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>établissement de pharmacologie</t>
+          <t>pharmacy facility</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Un établissement de santé qui a pour fonction d'entreposer, préparer, distribuer et surveiller l'utilisation des médicaments parmi les patients d'une zone géographique donnée ou suivis dans une organisation de soin donnée.</t>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t xml:space="preserve">Valence is a process profile of an emotion, mood, or affective bodily feeling (such as pleasure and pain). Valence can be positive or negative, with different strengths in both directions. For example, pleasure is positively valenced while pain is negatively valenced.  </t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">An affective process is any process that has positive or negative valence. </t>
+          <t>A mental process that has positive or negative valence.</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Genuss</t>
+          <t>jouissance</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -5217,7 +5217,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>An &lt;affective process&gt; that involves the experience of internal or external sensory stimuli.</t>
+          <t>An affective process that involves the experience of internal or external sensory stimuli.</t>
         </is>
       </c>
     </row>
